--- a/data/app_ui/uu_ui/1_register.xlsx
+++ b/data/app_ui/uu_ui/1_register.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180" tabRatio="434"/>
+    <workbookView windowWidth="27040" windowHeight="11020" tabRatio="434"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="143">
   <si>
     <t>case_module</t>
   </si>
@@ -44,6 +44,9 @@
     <t>skip</t>
   </si>
   <si>
+    <t>page_object</t>
+  </si>
+  <si>
     <t>by</t>
   </si>
   <si>
@@ -56,10 +59,13 @@
     <t>value</t>
   </si>
   <si>
+    <t>assertion_type</t>
+  </si>
+  <si>
     <t>deposit</t>
   </si>
   <si>
-    <t>retrieve</t>
+    <t>extract_var</t>
   </si>
   <si>
     <t>expected</t>
@@ -69,6 +75,9 @@
   </si>
   <si>
     <t>wait</t>
+  </si>
+  <si>
+    <t>screenshot</t>
   </si>
   <si>
     <t>介绍页：第一页文本检测</t>
@@ -455,16 +464,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -478,7 +487,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -486,14 +495,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -501,7 +510,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -509,7 +518,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -517,7 +526,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -525,7 +534,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -533,14 +542,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -548,7 +557,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -556,7 +565,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -564,14 +573,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -579,42 +588,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -934,19 +943,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1092,17 +1101,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1113,55 +1122,55 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
@@ -1459,26 +1468,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N163"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <dimension ref="A1:Q163"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="15.7142857142857" style="3" customWidth="1"/>
+    <col min="1" max="1" width="15.7115384615385" style="3" customWidth="1"/>
     <col min="2" max="2" width="20" style="3" customWidth="1"/>
-    <col min="3" max="3" width="23.8761904761905" style="5" customWidth="1"/>
-    <col min="4" max="4" width="33.8761904761905" style="6" customWidth="1"/>
-    <col min="5" max="5" width="5.71428571428571" style="3" customWidth="1"/>
-    <col min="6" max="6" width="10.8761904761905" style="3" customWidth="1"/>
-    <col min="7" max="7" width="50.752380952381" style="3" customWidth="1"/>
-    <col min="8" max="8" width="25" style="3" customWidth="1"/>
-    <col min="9" max="9" width="37" style="3" customWidth="1"/>
-    <col min="10" max="10" width="8.5047619047619" style="3" customWidth="1"/>
-    <col min="11" max="11" width="9.38095238095238" style="3" customWidth="1"/>
-    <col min="12" max="12" width="54.3714285714286" style="3" customWidth="1"/>
-    <col min="13" max="13" width="18.3714285714286" style="3" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="3"/>
+    <col min="3" max="3" width="23.875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="33.875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="5.71153846153846" style="3" customWidth="1"/>
+    <col min="6" max="6" width="14.9230769230769" style="3" customWidth="1"/>
+    <col min="7" max="7" width="10.875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="50.75" style="3" customWidth="1"/>
+    <col min="9" max="9" width="25" style="3" customWidth="1"/>
+    <col min="10" max="10" width="37" style="3" customWidth="1"/>
+    <col min="11" max="11" width="17.6153846153846" style="3" customWidth="1"/>
+    <col min="12" max="12" width="8.5" style="3" customWidth="1"/>
+    <col min="13" max="13" width="9.38461538461539" style="3" customWidth="1"/>
+    <col min="14" max="14" width="54.375" style="3" customWidth="1"/>
+    <col min="15" max="15" width="18.375" style="3" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:14">
+    <row r="1" s="1" customFormat="1" ht="17" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1494,16 +1505,16 @@
       <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="7" t="s">
@@ -1512,3270 +1523,3594 @@
       <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="L1" s="7" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="12" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="3:12">
+      <c r="O1" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" ht="17" spans="3:14">
       <c r="C2" s="5">
         <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="8"/>
-      <c r="F2" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
       <c r="G2" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="5"/>
+        <v>20</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="K2" s="5"/>
-      <c r="L2" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" ht="49.5" spans="4:12">
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" ht="51" spans="4:14">
       <c r="D3" s="5"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
       <c r="G3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" s="5"/>
+      <c r="J3" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="K3" s="5"/>
-      <c r="L3" s="11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="3:12">
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="3:14">
       <c r="C4" s="5">
         <v>2</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
       <c r="G4" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="5"/>
+        <v>26</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
-      <c r="L4" s="11"/>
-    </row>
-    <row r="5" spans="4:12">
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="9"/>
+    </row>
+    <row r="5" ht="17" spans="4:14">
       <c r="D5" s="5"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
       <c r="G5" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" s="5"/>
+        <v>20</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="K5" s="5"/>
-      <c r="L5" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" ht="49.5" spans="4:12">
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" ht="51" spans="4:14">
       <c r="D6" s="5"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
       <c r="G6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6" s="5"/>
+      <c r="J6" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="K6" s="5"/>
-      <c r="L6" s="11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="3:12">
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="3:14">
       <c r="C7" s="5">
         <v>3</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
       <c r="G7" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I7" s="5"/>
+        <v>26</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
-      <c r="L7" s="11"/>
-    </row>
-    <row r="8" spans="4:12">
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="9"/>
+    </row>
+    <row r="8" ht="17" spans="4:14">
       <c r="D8" s="5"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
       <c r="G8" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J8" s="5"/>
+        <v>20</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="K8" s="5"/>
-      <c r="L8" s="11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" ht="49.5" spans="4:12">
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" ht="51" spans="4:14">
       <c r="D9" s="5"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
       <c r="G9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9" s="5"/>
+      <c r="J9" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="K9" s="5"/>
-      <c r="L9" s="11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="3:12">
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="3:14">
       <c r="C10" s="5">
         <v>4</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
       <c r="G10" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I10" s="5"/>
+        <v>26</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
-      <c r="L10" s="11"/>
-    </row>
-    <row r="11" spans="4:12">
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="9"/>
+    </row>
+    <row r="11" ht="17" spans="4:14">
       <c r="D11" s="5"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
       <c r="G11" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J11" s="5"/>
+        <v>20</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="K11" s="5"/>
-      <c r="L11" s="11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" ht="49.5" spans="4:12">
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" ht="51" spans="4:14">
       <c r="D12" s="5"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
       <c r="G12" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I12" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H12" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J12" s="5"/>
+      <c r="J12" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="K12" s="5"/>
-      <c r="L12" s="11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="3:12">
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="3:14">
       <c r="C13" s="5">
         <v>5</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="8"/>
-      <c r="F13" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
       <c r="G13" s="5" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I13" s="5"/>
+        <v>37</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
-      <c r="L13" s="11"/>
-    </row>
-    <row r="14" s="2" customFormat="1" spans="3:12">
-      <c r="C14" s="9">
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="9"/>
+    </row>
+    <row r="14" s="2" customFormat="1" spans="3:14">
+      <c r="C14" s="8">
         <v>6</v>
       </c>
-      <c r="D14" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="13"/>
-    </row>
-    <row r="15" spans="3:14">
+      <c r="D14" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="13"/>
+    </row>
+    <row r="15" spans="3:16">
       <c r="C15" s="5">
         <v>7</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
       <c r="G15" s="5" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="N15" s="3">
+        <v>41</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P15" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="3:9">
+    <row r="16" spans="3:10">
       <c r="C16" s="5">
         <v>8</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E16" s="8"/>
-      <c r="F16" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I16" s="14" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="17" spans="4:11">
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J16" s="14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="4:13">
       <c r="D17" s="5"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
       <c r="G17" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I17" s="5"/>
+        <v>26</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
-    </row>
-    <row r="18" spans="4:12">
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+    </row>
+    <row r="18" ht="17" spans="4:14">
       <c r="D18" s="5"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
       <c r="G18" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J18" s="5"/>
+        <v>20</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="K18" s="5"/>
-      <c r="L18" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="3:8">
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="3:9">
       <c r="C19" s="5">
         <v>9</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E19" s="8"/>
-      <c r="F19" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="20" spans="4:9">
+        <v>49</v>
+      </c>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="4:11">
       <c r="D20" s="5"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>41</v>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21" spans="4:11">
+        <v>44</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="K20" s="5"/>
+    </row>
+    <row r="21" spans="4:13">
       <c r="D21" s="5"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
       <c r="G21" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I21" s="5"/>
+        <v>26</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
-    </row>
-    <row r="22" s="3" customFormat="1" spans="3:12">
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+    </row>
+    <row r="22" s="3" customFormat="1" spans="3:14">
       <c r="C22" s="5">
         <v>10</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E22" s="8"/>
-      <c r="F22" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
       <c r="G22" s="5" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J22" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="K22" s="5"/>
-      <c r="L22" s="11"/>
-    </row>
-    <row r="23" s="3" customFormat="1" spans="3:12">
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="9"/>
+    </row>
+    <row r="23" s="3" customFormat="1" spans="3:14">
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
       <c r="G23" s="5" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I23" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
-      <c r="L23" s="11"/>
-    </row>
-    <row r="24" s="3" customFormat="1" spans="3:12">
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="9"/>
+    </row>
+    <row r="24" s="3" customFormat="1" spans="3:14">
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
       <c r="G24" s="5" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="J24" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="K24" s="5"/>
-      <c r="L24" s="11"/>
-    </row>
-    <row r="25" s="3" customFormat="1" spans="3:12">
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="9"/>
+    </row>
+    <row r="25" s="3" customFormat="1" spans="3:14">
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
       <c r="G25" s="5" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I25" s="5"/>
+        <v>58</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
-      <c r="L25" s="11"/>
-    </row>
-    <row r="26" s="3" customFormat="1" spans="3:12">
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="9"/>
+    </row>
+    <row r="26" s="3" customFormat="1" spans="3:14">
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
       <c r="G26" s="5" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I26" s="5"/>
+        <v>59</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
-      <c r="L26" s="11"/>
-    </row>
-    <row r="27" s="3" customFormat="1" spans="3:12">
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="9"/>
+    </row>
+    <row r="27" s="3" customFormat="1" ht="17" spans="3:14">
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
       <c r="G27" s="5" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J27" s="5"/>
+        <v>20</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="K27" s="5"/>
-      <c r="L27" s="11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="28" spans="3:12">
-      <c r="C28" s="11">
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14">
+      <c r="C28" s="9">
         <v>11</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E28" s="8"/>
-      <c r="F28" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
       <c r="G28" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I28" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="H28" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I28" s="5"/>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
-      <c r="L28" s="11"/>
-    </row>
-    <row r="29" spans="3:12">
-      <c r="C29" s="11"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="9"/>
+    </row>
+    <row r="29" spans="3:14">
+      <c r="C29" s="9"/>
       <c r="D29" s="5"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
       <c r="G29" s="5" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I29" s="5"/>
+        <v>56</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
-      <c r="L29" s="11"/>
-    </row>
-    <row r="30" spans="3:12">
-      <c r="C30" s="11"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="9"/>
+    </row>
+    <row r="30" spans="3:14">
+      <c r="C30" s="9"/>
       <c r="D30" s="5"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
       <c r="G30" s="5" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J30" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="K30" s="5"/>
-      <c r="L30" s="11"/>
-    </row>
-    <row r="31" spans="3:12">
-      <c r="C31" s="11"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="9"/>
+    </row>
+    <row r="31" spans="3:14">
+      <c r="C31" s="9"/>
       <c r="D31" s="5"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
       <c r="G31" s="5" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J31" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="K31" s="5"/>
-      <c r="L31" s="11"/>
-    </row>
-    <row r="32" spans="3:12">
-      <c r="C32" s="11"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="9"/>
+    </row>
+    <row r="32" spans="3:14">
+      <c r="C32" s="9"/>
       <c r="D32" s="5"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
       <c r="G32" s="5" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I32" s="5"/>
+        <v>59</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J32" s="5"/>
       <c r="K32" s="5"/>
-      <c r="L32" s="11"/>
-    </row>
-    <row r="33" spans="3:12">
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="9"/>
+    </row>
+    <row r="33" spans="3:14">
       <c r="C33" s="5">
         <v>12</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E33" s="8"/>
-      <c r="F33" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
       <c r="G33" s="5" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I33" s="5">
+        <v>64</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J33" s="5">
         <v>123466</v>
       </c>
-      <c r="J33" s="5"/>
       <c r="K33" s="5"/>
-      <c r="L33" s="11"/>
-    </row>
-    <row r="34" spans="4:12">
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="9"/>
+    </row>
+    <row r="34" spans="4:14">
       <c r="D34" s="5"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
       <c r="G34" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I34" s="5"/>
+        <v>26</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J34" s="5"/>
       <c r="K34" s="5"/>
-      <c r="L34" s="11"/>
-    </row>
-    <row r="35" spans="4:12">
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="9"/>
+    </row>
+    <row r="35" ht="17" spans="4:14">
       <c r="D35" s="5"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
       <c r="G35" s="5" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J35" s="5"/>
+        <v>20</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="K35" s="5"/>
-      <c r="L35" s="11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="36" spans="3:12">
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="36" spans="3:14">
       <c r="C36" s="5">
         <v>13</v>
       </c>
       <c r="D36" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H36" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E36" s="8"/>
-      <c r="F36" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I36" s="5"/>
+      <c r="I36" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
-      <c r="L36" s="11"/>
-    </row>
-    <row r="37" ht="49.5" spans="4:12">
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="9"/>
+    </row>
+    <row r="37" ht="68" spans="4:14">
       <c r="D37" s="5"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
       <c r="G37" s="5" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="J37" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>68</v>
+      </c>
       <c r="K37" s="5"/>
-      <c r="L37" s="11" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="38" spans="4:12">
+      <c r="L37" s="5"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="38" spans="4:14">
       <c r="D38" s="5"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
       <c r="G38" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I38" s="5"/>
+        <v>26</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
-      <c r="L38" s="11"/>
-    </row>
-    <row r="39" spans="3:12">
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="9"/>
+    </row>
+    <row r="39" spans="3:14">
       <c r="C39" s="5">
         <v>14</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E39" s="8"/>
-      <c r="F39" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="E39" s="10"/>
+      <c r="F39" s="10"/>
       <c r="G39" s="5" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="J39" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J39" s="5" t="s">
+        <v>72</v>
+      </c>
       <c r="K39" s="5"/>
-      <c r="L39" s="11"/>
-    </row>
-    <row r="40" spans="4:12">
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="9"/>
+    </row>
+    <row r="40" spans="4:14">
       <c r="D40" s="5"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E40" s="10"/>
+      <c r="F40" s="10"/>
       <c r="G40" s="5" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I40" s="5"/>
+        <v>73</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
-      <c r="L40" s="11"/>
-    </row>
-    <row r="41" spans="3:12">
+      <c r="L40" s="5"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="9"/>
+    </row>
+    <row r="41" spans="3:14">
       <c r="C41" s="5">
         <v>15</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="E41" s="8"/>
-      <c r="F41" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
       <c r="G41" s="5" t="s">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I41" s="5"/>
+        <v>75</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
-      <c r="L41" s="11"/>
-    </row>
-    <row r="42" spans="3:12">
+      <c r="L41" s="5"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="9"/>
+    </row>
+    <row r="42" spans="3:14">
       <c r="C42" s="5">
         <v>16</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E42" s="8"/>
-      <c r="F42" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
       <c r="G42" s="5" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I42" s="5"/>
+        <v>77</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
-      <c r="L42" s="11"/>
-    </row>
-    <row r="43" spans="4:12">
+      <c r="L42" s="5"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="9"/>
+    </row>
+    <row r="43" spans="4:14">
       <c r="D43" s="5"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
       <c r="G43" s="5" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I43" s="5"/>
+        <v>78</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J43" s="5"/>
       <c r="K43" s="5"/>
-      <c r="L43" s="11"/>
-    </row>
-    <row r="44" spans="4:12">
+      <c r="L43" s="5"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="9"/>
+    </row>
+    <row r="44" spans="4:14">
       <c r="D44" s="5"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E44" s="10"/>
+      <c r="F44" s="10"/>
       <c r="G44" s="5" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I44" s="5"/>
+        <v>79</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J44" s="5"/>
       <c r="K44" s="5"/>
-      <c r="L44" s="11"/>
-    </row>
-    <row r="45" s="2" customFormat="1" spans="3:12">
-      <c r="C45" s="9">
+      <c r="L44" s="5"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="9"/>
+    </row>
+    <row r="45" s="2" customFormat="1" spans="3:14">
+      <c r="C45" s="8">
         <v>17</v>
       </c>
-      <c r="D45" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="E45" s="10"/>
-      <c r="F45" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="I45" s="9"/>
-      <c r="J45" s="9"/>
-      <c r="K45" s="9"/>
-      <c r="L45" s="13"/>
-    </row>
-    <row r="46" s="2" customFormat="1" spans="3:14">
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G46" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="H46" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="I46" s="9"/>
-      <c r="J46" s="9"/>
-      <c r="K46" s="9"/>
-      <c r="L46" s="13"/>
-      <c r="N46" s="2">
+      <c r="D45" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="J45" s="8"/>
+      <c r="K45" s="8"/>
+      <c r="L45" s="8"/>
+      <c r="M45" s="8"/>
+      <c r="N45" s="13"/>
+    </row>
+    <row r="46" s="2" customFormat="1" spans="3:16">
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="J46" s="8"/>
+      <c r="K46" s="8"/>
+      <c r="L46" s="8"/>
+      <c r="M46" s="8"/>
+      <c r="N46" s="13"/>
+      <c r="P46" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="3:12">
+    <row r="47" spans="3:14">
       <c r="C47" s="5">
         <v>18</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E47" s="8"/>
-      <c r="F47" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H47" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="J47" s="5"/>
-      <c r="K47" s="5"/>
-      <c r="L47" s="11"/>
-    </row>
-    <row r="48" spans="4:12">
+        <v>49</v>
+      </c>
+      <c r="E47" s="10"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L47" s="5"/>
+      <c r="M47" s="5"/>
+      <c r="N47" s="9"/>
+    </row>
+    <row r="48" spans="4:14">
       <c r="D48" s="5"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H48" s="5" t="s">
-        <v>41</v>
+      <c r="E48" s="10"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="J48" s="5"/>
-      <c r="K48" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="L48" s="11"/>
-    </row>
-    <row r="49" spans="4:12">
+        <v>44</v>
+      </c>
+      <c r="J48" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="K48" s="5"/>
+      <c r="L48" s="5"/>
+      <c r="M48" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="N48" s="9"/>
+    </row>
+    <row r="49" spans="4:14">
       <c r="D49" s="5"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E49" s="10"/>
+      <c r="F49" s="10"/>
       <c r="G49" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I49" s="5"/>
+        <v>26</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J49" s="5"/>
       <c r="K49" s="5"/>
-      <c r="L49" s="11"/>
-    </row>
-    <row r="50" spans="3:12">
+      <c r="L49" s="5"/>
+      <c r="M49" s="5"/>
+      <c r="N49" s="9"/>
+    </row>
+    <row r="50" spans="3:14">
       <c r="C50" s="5">
         <v>19</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E50" s="8"/>
-      <c r="F50" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="E50" s="10"/>
+      <c r="F50" s="10"/>
       <c r="G50" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H50" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I50" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="H50" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I50" s="5"/>
       <c r="J50" s="5"/>
       <c r="K50" s="5"/>
-      <c r="L50" s="11"/>
-    </row>
-    <row r="51" spans="4:12">
+      <c r="L50" s="5"/>
+      <c r="M50" s="5"/>
+      <c r="N50" s="9"/>
+    </row>
+    <row r="51" spans="4:14">
       <c r="D51" s="5"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E51" s="10"/>
+      <c r="F51" s="10"/>
       <c r="G51" s="5" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I51" s="5"/>
+        <v>56</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="J51" s="5"/>
       <c r="K51" s="5"/>
-      <c r="L51" s="11"/>
-    </row>
-    <row r="52" spans="4:12">
+      <c r="L51" s="5"/>
+      <c r="M51" s="5"/>
+      <c r="N51" s="9"/>
+    </row>
+    <row r="52" spans="4:14">
       <c r="D52" s="5"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E52" s="10"/>
+      <c r="F52" s="10"/>
       <c r="G52" s="5" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J52" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J52" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="K52" s="5"/>
-      <c r="L52" s="11"/>
-    </row>
-    <row r="53" spans="4:12">
+      <c r="L52" s="5"/>
+      <c r="M52" s="5"/>
+      <c r="N52" s="9"/>
+    </row>
+    <row r="53" spans="4:14">
       <c r="D53" s="5"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E53" s="10"/>
+      <c r="F53" s="10"/>
       <c r="G53" s="5" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J53" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="K53" s="5"/>
-      <c r="L53" s="11"/>
-    </row>
-    <row r="54" spans="4:12">
+      <c r="L53" s="5"/>
+      <c r="M53" s="5"/>
+      <c r="N53" s="9"/>
+    </row>
+    <row r="54" spans="4:14">
       <c r="D54" s="5"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E54" s="10"/>
+      <c r="F54" s="10"/>
       <c r="G54" s="5" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I54" s="5"/>
+        <v>59</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J54" s="5"/>
       <c r="K54" s="5"/>
-      <c r="L54" s="11"/>
-    </row>
-    <row r="55" spans="3:12">
+      <c r="L54" s="5"/>
+      <c r="M54" s="5"/>
+      <c r="N54" s="9"/>
+    </row>
+    <row r="55" spans="3:14">
       <c r="C55" s="5">
         <v>20</v>
       </c>
       <c r="D55" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E55" s="10"/>
+      <c r="F55" s="10"/>
+      <c r="G55" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H55" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E55" s="8"/>
-      <c r="F55" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G55" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H55" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I55" s="5"/>
+      <c r="I55" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="J55" s="5"/>
       <c r="K55" s="5"/>
-      <c r="L55" s="11"/>
-    </row>
-    <row r="56" ht="49.5" spans="4:12">
+      <c r="L55" s="5"/>
+      <c r="M55" s="5"/>
+      <c r="N55" s="9"/>
+    </row>
+    <row r="56" ht="68" spans="4:14">
       <c r="D56" s="5"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E56" s="10"/>
+      <c r="F56" s="10"/>
       <c r="G56" s="5" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="J56" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J56" s="5" t="s">
+        <v>68</v>
+      </c>
       <c r="K56" s="5"/>
-      <c r="L56" s="11" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="57" spans="4:12">
+      <c r="L56" s="5"/>
+      <c r="M56" s="5"/>
+      <c r="N56" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="57" spans="4:14">
       <c r="D57" s="5"/>
-      <c r="E57" s="8"/>
-      <c r="F57" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E57" s="10"/>
+      <c r="F57" s="10"/>
       <c r="G57" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I57" s="5"/>
+        <v>26</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J57" s="5"/>
       <c r="K57" s="5"/>
-      <c r="L57" s="11"/>
-    </row>
-    <row r="58" spans="3:12">
+      <c r="L57" s="5"/>
+      <c r="M57" s="5"/>
+      <c r="N57" s="9"/>
+    </row>
+    <row r="58" spans="3:14">
       <c r="C58" s="5">
         <v>21</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="E58" s="8"/>
-      <c r="F58" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="E58" s="10"/>
+      <c r="F58" s="10"/>
       <c r="G58" s="5" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I58" s="5"/>
+        <v>59</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J58" s="5"/>
       <c r="K58" s="5"/>
-      <c r="L58" s="11"/>
-    </row>
-    <row r="59" spans="3:12">
+      <c r="L58" s="5"/>
+      <c r="M58" s="5"/>
+      <c r="N58" s="9"/>
+    </row>
+    <row r="59" spans="3:14">
       <c r="C59" s="5">
         <v>22</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E59" s="8"/>
-      <c r="F59" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="E59" s="10"/>
+      <c r="F59" s="10"/>
       <c r="G59" s="5" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="J59" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J59" s="5" t="s">
+        <v>85</v>
+      </c>
       <c r="K59" s="5"/>
-      <c r="L59" s="11"/>
-    </row>
-    <row r="60" spans="4:12">
+      <c r="L59" s="5"/>
+      <c r="M59" s="5"/>
+      <c r="N59" s="9"/>
+    </row>
+    <row r="60" spans="4:14">
       <c r="D60" s="5"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E60" s="10"/>
+      <c r="F60" s="10"/>
       <c r="G60" s="5" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I60" s="5"/>
+        <v>73</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J60" s="5"/>
       <c r="K60" s="5"/>
-      <c r="L60" s="11"/>
-    </row>
-    <row r="61" spans="4:12">
+      <c r="L60" s="5"/>
+      <c r="M60" s="5"/>
+      <c r="N60" s="9"/>
+    </row>
+    <row r="61" ht="17" spans="4:14">
       <c r="D61" s="5"/>
-      <c r="E61" s="8"/>
-      <c r="F61" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="E61" s="10"/>
+      <c r="F61" s="10"/>
       <c r="G61" s="5" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="I61" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J61" s="5"/>
+        <v>20</v>
+      </c>
+      <c r="J61" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="K61" s="5"/>
-      <c r="L61" s="11" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="62" spans="3:12">
+      <c r="L61" s="5"/>
+      <c r="M61" s="5"/>
+      <c r="N61" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14">
       <c r="C62" s="5">
         <v>23</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E62" s="8"/>
-      <c r="F62" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="E62" s="10"/>
+      <c r="F62" s="10"/>
       <c r="G62" s="5" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="I62" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="J62" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J62" s="5" t="s">
+        <v>89</v>
+      </c>
       <c r="K62" s="5"/>
-      <c r="L62" s="11"/>
-    </row>
-    <row r="63" spans="4:12">
+      <c r="L62" s="5"/>
+      <c r="M62" s="5"/>
+      <c r="N62" s="9"/>
+    </row>
+    <row r="63" spans="4:14">
       <c r="D63" s="5"/>
-      <c r="E63" s="8"/>
-      <c r="F63" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E63" s="10"/>
+      <c r="F63" s="10"/>
       <c r="G63" s="5" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="I63" s="5"/>
+        <v>73</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="J63" s="5"/>
       <c r="K63" s="5"/>
-      <c r="L63" s="11" t="b">
+      <c r="L63" s="5"/>
+      <c r="M63" s="5"/>
+      <c r="N63" s="9" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="3:12">
+    <row r="64" spans="3:14">
       <c r="C64" s="5">
         <v>24</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="E64" s="8"/>
-      <c r="F64" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="E64" s="10"/>
+      <c r="F64" s="10"/>
       <c r="G64" s="5" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="J64" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J64" s="5" t="s">
+        <v>92</v>
+      </c>
       <c r="K64" s="5"/>
-      <c r="L64" s="11"/>
-    </row>
-    <row r="65" spans="4:12">
+      <c r="L64" s="5"/>
+      <c r="M64" s="5"/>
+      <c r="N64" s="9"/>
+    </row>
+    <row r="65" spans="4:14">
       <c r="D65" s="5"/>
-      <c r="E65" s="8"/>
-      <c r="F65" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E65" s="10"/>
+      <c r="F65" s="10"/>
       <c r="G65" s="5" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I65" s="5"/>
+        <v>73</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J65" s="5"/>
       <c r="K65" s="5"/>
-      <c r="L65" s="11"/>
-    </row>
-    <row r="66" ht="33" spans="4:12">
+      <c r="L65" s="5"/>
+      <c r="M65" s="5"/>
+      <c r="N65" s="9"/>
+    </row>
+    <row r="66" ht="34" spans="4:14">
       <c r="D66" s="5"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="E66" s="10"/>
+      <c r="F66" s="10"/>
       <c r="G66" s="5" t="s">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J66" s="5"/>
+        <v>20</v>
+      </c>
+      <c r="J66" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="K66" s="5"/>
-      <c r="L66" s="11" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="67" spans="3:12">
+      <c r="L66" s="5"/>
+      <c r="M66" s="5"/>
+      <c r="N66" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="67" spans="3:14">
       <c r="C67" s="5">
         <v>25</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E67" s="8"/>
-      <c r="F67" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="E67" s="10"/>
+      <c r="F67" s="10"/>
       <c r="G67" s="5" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="J67" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J67" s="5" t="s">
+        <v>72</v>
+      </c>
       <c r="K67" s="5"/>
-      <c r="L67" s="11"/>
-    </row>
-    <row r="68" spans="3:12">
+      <c r="L67" s="5"/>
+      <c r="M67" s="5"/>
+      <c r="N67" s="9"/>
+    </row>
+    <row r="68" spans="3:14">
       <c r="C68" s="5">
         <v>26</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="E68" s="8"/>
-      <c r="F68" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="E68" s="10"/>
+      <c r="F68" s="10"/>
       <c r="G68" s="5" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I68" s="5"/>
+        <v>73</v>
+      </c>
+      <c r="I68" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J68" s="5"/>
       <c r="K68" s="5"/>
-      <c r="L68" s="11"/>
-    </row>
-    <row r="69" s="2" customFormat="1" spans="3:12">
-      <c r="C69" s="9">
-        <v>27</v>
-      </c>
-      <c r="D69" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="E69" s="10"/>
-      <c r="F69" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G69" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="I69" s="9"/>
-      <c r="J69" s="9"/>
-      <c r="K69" s="9"/>
-      <c r="L69" s="13"/>
-    </row>
-    <row r="70" s="2" customFormat="1" spans="3:12">
-      <c r="C70" s="9"/>
-      <c r="D70" s="9"/>
-      <c r="E70" s="10"/>
-      <c r="F70" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G70" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H70" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="I70" s="9"/>
-      <c r="J70" s="9"/>
-      <c r="K70" s="9"/>
-      <c r="L70" s="13"/>
-    </row>
-    <row r="71" s="2" customFormat="1" spans="3:12">
-      <c r="C71" s="9"/>
-      <c r="D71" s="9"/>
-      <c r="E71" s="10"/>
-      <c r="F71" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G71" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="I71" s="9"/>
-      <c r="J71" s="9"/>
-      <c r="K71" s="9"/>
-      <c r="L71" s="13"/>
-    </row>
-    <row r="72" spans="3:12">
+      <c r="L68" s="5"/>
+      <c r="M68" s="5"/>
+      <c r="N68" s="9"/>
+    </row>
+    <row r="69" s="2" customFormat="1" spans="3:14">
+      <c r="C69" s="8">
+        <v>27</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E69" s="11"/>
+      <c r="F69" s="11"/>
+      <c r="G69" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H69" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="I69" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="J69" s="8"/>
+      <c r="K69" s="8"/>
+      <c r="L69" s="8"/>
+      <c r="M69" s="8"/>
+      <c r="N69" s="13"/>
+    </row>
+    <row r="70" s="2" customFormat="1" spans="3:14">
+      <c r="C70" s="8"/>
+      <c r="D70" s="8"/>
+      <c r="E70" s="11"/>
+      <c r="F70" s="11"/>
+      <c r="G70" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H70" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="I70" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="J70" s="8"/>
+      <c r="K70" s="8"/>
+      <c r="L70" s="8"/>
+      <c r="M70" s="8"/>
+      <c r="N70" s="13"/>
+    </row>
+    <row r="71" s="2" customFormat="1" spans="3:14">
+      <c r="C71" s="8"/>
+      <c r="D71" s="8"/>
+      <c r="E71" s="11"/>
+      <c r="F71" s="11"/>
+      <c r="G71" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H71" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="I71" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="J71" s="8"/>
+      <c r="K71" s="8"/>
+      <c r="L71" s="8"/>
+      <c r="M71" s="8"/>
+      <c r="N71" s="13"/>
+    </row>
+    <row r="72" spans="3:14">
       <c r="C72" s="5">
         <v>28</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E72" s="8"/>
-      <c r="F72" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="E72" s="10"/>
+      <c r="F72" s="10"/>
       <c r="G72" s="5" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I72" s="5"/>
+        <v>99</v>
+      </c>
+      <c r="I72" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J72" s="5"/>
       <c r="K72" s="5"/>
-      <c r="L72" s="11"/>
-    </row>
-    <row r="73" ht="24" customHeight="1" spans="4:12">
+      <c r="L72" s="5"/>
+      <c r="M72" s="5"/>
+      <c r="N72" s="9"/>
+    </row>
+    <row r="73" ht="24" customHeight="1" spans="4:14">
       <c r="D73" s="5"/>
-      <c r="E73" s="8"/>
-      <c r="F73" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E73" s="10"/>
+      <c r="F73" s="10"/>
       <c r="G73" s="5" t="s">
-        <v>97</v>
+        <v>18</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I73" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J73" s="5"/>
-      <c r="K73" s="5"/>
-      <c r="L73" s="11"/>
-    </row>
-    <row r="74" spans="3:12">
+        <v>100</v>
+      </c>
+      <c r="I73" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J73" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="K73" s="9"/>
+      <c r="L73" s="5"/>
+      <c r="M73" s="5"/>
+      <c r="N73" s="9"/>
+    </row>
+    <row r="74" spans="3:14">
       <c r="C74" s="5">
         <v>29</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E74" s="8"/>
-      <c r="F74" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="E74" s="10"/>
+      <c r="F74" s="10"/>
       <c r="G74" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I74" s="5"/>
+        <v>26</v>
+      </c>
+      <c r="I74" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J74" s="5"/>
       <c r="K74" s="5"/>
-      <c r="L74" s="11"/>
-    </row>
-    <row r="75" spans="4:12">
+      <c r="L74" s="5"/>
+      <c r="M74" s="5"/>
+      <c r="N74" s="9"/>
+    </row>
+    <row r="75" spans="4:14">
       <c r="D75" s="5"/>
-      <c r="E75" s="8"/>
-      <c r="F75" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E75" s="10"/>
+      <c r="F75" s="10"/>
       <c r="G75" s="5" t="s">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I75" s="5"/>
+        <v>103</v>
+      </c>
+      <c r="I75" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J75" s="5"/>
       <c r="K75" s="5"/>
-      <c r="L75" s="11"/>
-    </row>
-    <row r="76" spans="4:12">
+      <c r="L75" s="5"/>
+      <c r="M75" s="5"/>
+      <c r="N75" s="9"/>
+    </row>
+    <row r="76" spans="4:14">
       <c r="D76" s="5"/>
-      <c r="E76" s="8"/>
-      <c r="F76" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E76" s="10"/>
+      <c r="F76" s="10"/>
       <c r="G76" s="5" t="s">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I76" s="5"/>
+        <v>104</v>
+      </c>
+      <c r="I76" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J76" s="5"/>
       <c r="K76" s="5"/>
-      <c r="L76" s="11"/>
-    </row>
-    <row r="77" spans="4:12">
+      <c r="L76" s="5"/>
+      <c r="M76" s="5"/>
+      <c r="N76" s="9"/>
+    </row>
+    <row r="77" spans="4:14">
       <c r="D77" s="5"/>
-      <c r="E77" s="8"/>
-      <c r="F77" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E77" s="10"/>
+      <c r="F77" s="10"/>
       <c r="G77" s="5" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I77" s="5"/>
+        <v>105</v>
+      </c>
+      <c r="I77" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J77" s="5"/>
       <c r="K77" s="5"/>
-      <c r="L77" s="11"/>
-    </row>
-    <row r="78" spans="3:12">
+      <c r="L77" s="5"/>
+      <c r="M77" s="5"/>
+      <c r="N77" s="9"/>
+    </row>
+    <row r="78" spans="3:14">
       <c r="C78" s="5">
         <v>30</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="E78" s="8"/>
-      <c r="F78" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="E78" s="10"/>
+      <c r="F78" s="10"/>
       <c r="G78" s="5" t="s">
-        <v>104</v>
+        <v>18</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I78" s="5">
+        <v>107</v>
+      </c>
+      <c r="I78" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J78" s="5">
         <v>123456</v>
       </c>
-      <c r="J78" s="5"/>
       <c r="K78" s="5"/>
-      <c r="L78" s="11"/>
-    </row>
-    <row r="79" spans="4:12">
+      <c r="L78" s="5"/>
+      <c r="M78" s="5"/>
+      <c r="N78" s="9"/>
+    </row>
+    <row r="79" spans="4:14">
       <c r="D79" s="5"/>
-      <c r="E79" s="8"/>
-      <c r="F79" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E79" s="10"/>
+      <c r="F79" s="10"/>
       <c r="G79" s="5" t="s">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I79" s="5"/>
+        <v>108</v>
+      </c>
+      <c r="I79" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J79" s="5"/>
       <c r="K79" s="5"/>
-      <c r="L79" s="11"/>
-    </row>
-    <row r="80" spans="4:12">
+      <c r="L79" s="5"/>
+      <c r="M79" s="5"/>
+      <c r="N79" s="9"/>
+    </row>
+    <row r="80" ht="17" spans="4:14">
       <c r="D80" s="5"/>
-      <c r="E80" s="8"/>
-      <c r="F80" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="H80" s="5" t="s">
-        <v>17</v>
+      <c r="E80" s="10"/>
+      <c r="F80" s="10"/>
+      <c r="G80" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>109</v>
       </c>
       <c r="I80" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J80" s="5"/>
+        <v>20</v>
+      </c>
+      <c r="J80" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="K80" s="5"/>
-      <c r="L80" s="11" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="81" spans="3:12">
+      <c r="L80" s="5"/>
+      <c r="M80" s="5"/>
+      <c r="N80" s="9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="81" spans="3:14">
       <c r="C81" s="5">
         <v>31</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="E81" s="8"/>
-      <c r="F81" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="E81" s="10"/>
+      <c r="F81" s="10"/>
       <c r="G81" s="5" t="s">
-        <v>104</v>
+        <v>18</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I81" s="5"/>
+        <v>107</v>
+      </c>
+      <c r="I81" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="J81" s="5"/>
       <c r="K81" s="5"/>
-      <c r="L81" s="11"/>
-    </row>
-    <row r="82" ht="49.5" spans="4:14">
+      <c r="L81" s="5"/>
+      <c r="M81" s="5"/>
+      <c r="N81" s="9"/>
+    </row>
+    <row r="82" ht="68" spans="4:16">
       <c r="D82" s="5"/>
-      <c r="E82" s="8"/>
-      <c r="F82" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E82" s="10"/>
+      <c r="F82" s="10"/>
       <c r="G82" s="5" t="s">
-        <v>104</v>
+        <v>18</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>41</v>
+        <v>107</v>
       </c>
       <c r="I82" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="J82" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J82" s="5" t="s">
+        <v>68</v>
+      </c>
       <c r="K82" s="5"/>
-      <c r="L82" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="N82" s="3">
+      <c r="L82" s="5"/>
+      <c r="M82" s="5"/>
+      <c r="N82" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="P82" s="3">
         <v>8</v>
       </c>
     </row>
-    <row r="83" spans="4:12">
+    <row r="83" spans="4:14">
       <c r="D83" s="5"/>
-      <c r="E83" s="8"/>
-      <c r="F83" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E83" s="10"/>
+      <c r="F83" s="10"/>
       <c r="G83" s="5" t="s">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I83" s="5"/>
+        <v>108</v>
+      </c>
+      <c r="I83" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J83" s="5"/>
       <c r="K83" s="5"/>
-      <c r="L83" s="11"/>
-    </row>
-    <row r="84" spans="3:12">
+      <c r="L83" s="5"/>
+      <c r="M83" s="5"/>
+      <c r="N83" s="9"/>
+    </row>
+    <row r="84" spans="3:14">
       <c r="C84" s="5">
         <v>32</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E84" s="8"/>
-      <c r="F84" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="E84" s="10"/>
+      <c r="F84" s="10"/>
       <c r="G84" s="5" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I84" s="5">
+        <v>114</v>
+      </c>
+      <c r="I84" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J84" s="5">
         <v>123456</v>
       </c>
-      <c r="J84" s="5"/>
       <c r="K84" s="5"/>
-      <c r="L84" s="11"/>
-    </row>
-    <row r="85" spans="4:12">
+      <c r="L84" s="5"/>
+      <c r="M84" s="5"/>
+      <c r="N84" s="9"/>
+    </row>
+    <row r="85" spans="4:14">
       <c r="D85" s="5"/>
-      <c r="E85" s="8"/>
-      <c r="F85" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G85" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H85" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J85" s="5"/>
-      <c r="K85" s="5"/>
-      <c r="L85" s="11"/>
-    </row>
-    <row r="86" spans="4:12">
+      <c r="E85" s="10"/>
+      <c r="F85" s="10"/>
+      <c r="G85" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I85" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L85" s="5"/>
+      <c r="M85" s="5"/>
+      <c r="N85" s="9"/>
+    </row>
+    <row r="86" spans="4:14">
       <c r="D86" s="5"/>
-      <c r="E86" s="8"/>
-      <c r="F86" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E86" s="10"/>
+      <c r="F86" s="10"/>
       <c r="G86" s="5" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I86" s="5">
+        <v>114</v>
+      </c>
+      <c r="I86" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J86" s="5">
         <v>111111</v>
       </c>
-      <c r="J86" s="5"/>
       <c r="K86" s="5"/>
-      <c r="L86" s="11"/>
-    </row>
-    <row r="87" spans="4:12">
+      <c r="L86" s="5"/>
+      <c r="M86" s="5"/>
+      <c r="N86" s="9"/>
+    </row>
+    <row r="87" spans="4:14">
       <c r="D87" s="5"/>
-      <c r="E87" s="8"/>
-      <c r="F87" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G87" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H87" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I87" s="5"/>
+      <c r="E87" s="10"/>
+      <c r="F87" s="10"/>
+      <c r="G87" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I87" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J87" s="5"/>
       <c r="K87" s="5"/>
-      <c r="L87" s="11"/>
-    </row>
-    <row r="88" spans="4:12">
+      <c r="L87" s="5"/>
+      <c r="M87" s="5"/>
+      <c r="N87" s="9"/>
+    </row>
+    <row r="88" ht="17" spans="4:14">
       <c r="D88" s="5"/>
-      <c r="E88" s="8"/>
-      <c r="F88" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G88" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H88" s="5" t="s">
-        <v>17</v>
+      <c r="E88" s="10"/>
+      <c r="F88" s="10"/>
+      <c r="G88" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="I88" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J88" s="5"/>
+        <v>20</v>
+      </c>
+      <c r="J88" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="K88" s="5"/>
-      <c r="L88" s="11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="89" spans="4:12">
+      <c r="L88" s="5"/>
+      <c r="M88" s="5"/>
+      <c r="N88" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="89" spans="4:14">
       <c r="D89" s="5"/>
-      <c r="E89" s="8"/>
-      <c r="F89" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E89" s="10"/>
+      <c r="F89" s="10"/>
       <c r="G89" s="5" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="H89" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I89" s="5"/>
+        <v>114</v>
+      </c>
+      <c r="I89" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="J89" s="5"/>
       <c r="K89" s="5"/>
-      <c r="L89" s="11"/>
-    </row>
-    <row r="90" spans="4:12">
+      <c r="L89" s="5"/>
+      <c r="M89" s="5"/>
+      <c r="N89" s="9"/>
+    </row>
+    <row r="90" spans="4:14">
       <c r="D90" s="5"/>
-      <c r="E90" s="8"/>
-      <c r="F90" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E90" s="10"/>
+      <c r="F90" s="10"/>
       <c r="G90" s="5" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="H90" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I90" s="5">
+        <v>114</v>
+      </c>
+      <c r="I90" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J90" s="5">
         <v>123456</v>
       </c>
-      <c r="J90" s="5"/>
       <c r="K90" s="5"/>
-      <c r="L90" s="11"/>
-    </row>
-    <row r="91" spans="4:12">
+      <c r="L90" s="5"/>
+      <c r="M90" s="5"/>
+      <c r="N90" s="9"/>
+    </row>
+    <row r="91" spans="4:14">
       <c r="D91" s="5"/>
-      <c r="E91" s="8"/>
-      <c r="F91" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H91" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I91" s="5"/>
+      <c r="E91" s="10"/>
+      <c r="F91" s="10"/>
+      <c r="G91" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I91" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J91" s="5"/>
       <c r="K91" s="5"/>
-      <c r="L91" s="11"/>
-    </row>
-    <row r="92" spans="3:12">
+      <c r="L91" s="5"/>
+      <c r="M91" s="5"/>
+      <c r="N91" s="9"/>
+    </row>
+    <row r="92" spans="3:14">
       <c r="C92" s="5">
         <v>33</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="E92" s="8"/>
-      <c r="F92" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="E92" s="10"/>
+      <c r="F92" s="10"/>
       <c r="G92" s="5" t="s">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="H92" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I92" s="5"/>
+        <v>103</v>
+      </c>
+      <c r="I92" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J92" s="5"/>
       <c r="K92" s="5"/>
-      <c r="L92" s="11"/>
-    </row>
-    <row r="93" spans="4:12">
+      <c r="L92" s="5"/>
+      <c r="M92" s="5"/>
+      <c r="N92" s="9"/>
+    </row>
+    <row r="93" spans="4:14">
       <c r="D93" s="5"/>
-      <c r="E93" s="8"/>
-      <c r="F93" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E93" s="10"/>
+      <c r="F93" s="10"/>
       <c r="G93" s="5" t="s">
-        <v>113</v>
+        <v>18</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I93" s="5"/>
+        <v>116</v>
+      </c>
+      <c r="I93" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J93" s="5"/>
       <c r="K93" s="5"/>
-      <c r="L93" s="11"/>
-    </row>
-    <row r="94" spans="4:12">
+      <c r="L93" s="5"/>
+      <c r="M93" s="5"/>
+      <c r="N93" s="9"/>
+    </row>
+    <row r="94" spans="4:14">
       <c r="D94" s="5"/>
-      <c r="E94" s="8"/>
-      <c r="F94" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E94" s="10"/>
+      <c r="F94" s="10"/>
       <c r="G94" s="5" t="s">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="H94" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I94" s="5"/>
+        <v>103</v>
+      </c>
+      <c r="I94" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J94" s="5"/>
       <c r="K94" s="5"/>
-      <c r="L94" s="11"/>
-    </row>
-    <row r="95" spans="4:12">
+      <c r="L94" s="5"/>
+      <c r="M94" s="5"/>
+      <c r="N94" s="9"/>
+    </row>
+    <row r="95" spans="4:14">
       <c r="D95" s="5"/>
-      <c r="E95" s="8"/>
-      <c r="F95" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E95" s="10"/>
+      <c r="F95" s="10"/>
       <c r="G95" s="5" t="s">
-        <v>114</v>
+        <v>18</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I95" s="5"/>
+        <v>117</v>
+      </c>
+      <c r="I95" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J95" s="5"/>
       <c r="K95" s="5"/>
-      <c r="L95" s="11"/>
-    </row>
-    <row r="96" spans="4:12">
+      <c r="L95" s="5"/>
+      <c r="M95" s="5"/>
+      <c r="N95" s="9"/>
+    </row>
+    <row r="96" spans="4:14">
       <c r="D96" s="5"/>
-      <c r="E96" s="8"/>
-      <c r="F96" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E96" s="10"/>
+      <c r="F96" s="10"/>
       <c r="G96" s="5" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="H96" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I96" s="5">
+        <v>114</v>
+      </c>
+      <c r="I96" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J96" s="5">
         <v>123456</v>
       </c>
-      <c r="J96" s="5"/>
       <c r="K96" s="5"/>
-      <c r="L96" s="11"/>
-    </row>
-    <row r="97" spans="4:12">
+      <c r="L96" s="5"/>
+      <c r="M96" s="5"/>
+      <c r="N96" s="9"/>
+    </row>
+    <row r="97" spans="4:14">
       <c r="D97" s="5"/>
-      <c r="E97" s="8"/>
-      <c r="F97" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G97" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H97" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I97" s="5"/>
+      <c r="E97" s="10"/>
+      <c r="F97" s="10"/>
+      <c r="G97" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I97" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J97" s="5"/>
       <c r="K97" s="5"/>
-      <c r="L97" s="11"/>
-    </row>
-    <row r="98" s="2" customFormat="1" spans="3:12">
-      <c r="C98" s="9">
+      <c r="L97" s="5"/>
+      <c r="M97" s="5"/>
+      <c r="N97" s="9"/>
+    </row>
+    <row r="98" s="2" customFormat="1" spans="3:14">
+      <c r="C98" s="8">
         <v>34</v>
       </c>
-      <c r="D98" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="E98" s="10"/>
-      <c r="F98" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G98" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="H98" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="I98" s="9"/>
-      <c r="J98" s="9"/>
-      <c r="K98" s="9"/>
-      <c r="L98" s="13"/>
-    </row>
-    <row r="99" spans="3:12">
+      <c r="D98" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="E98" s="11"/>
+      <c r="F98" s="11"/>
+      <c r="G98" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H98" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I98" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="J98" s="8"/>
+      <c r="K98" s="8"/>
+      <c r="L98" s="8"/>
+      <c r="M98" s="8"/>
+      <c r="N98" s="13"/>
+    </row>
+    <row r="99" spans="3:14">
       <c r="C99" s="5">
         <v>35</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="E99" s="8"/>
-      <c r="F99" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G99" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H99" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J99" s="5"/>
-      <c r="K99" s="5"/>
-      <c r="L99" s="11"/>
-    </row>
-    <row r="100" spans="4:12">
+        <v>119</v>
+      </c>
+      <c r="E99" s="10"/>
+      <c r="F99" s="10"/>
+      <c r="G99" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I99" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L99" s="5"/>
+      <c r="M99" s="5"/>
+      <c r="N99" s="9"/>
+    </row>
+    <row r="100" spans="4:14">
       <c r="D100" s="5"/>
-      <c r="E100" s="8"/>
-      <c r="F100" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E100" s="10"/>
+      <c r="F100" s="10"/>
       <c r="G100" s="5" t="s">
-        <v>118</v>
+        <v>18</v>
       </c>
       <c r="H100" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I100" s="5">
+        <v>121</v>
+      </c>
+      <c r="I100" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J100" s="5">
         <v>63</v>
       </c>
-      <c r="J100" s="5"/>
       <c r="K100" s="5"/>
-      <c r="L100" s="11"/>
-    </row>
-    <row r="101" spans="4:12">
+      <c r="L100" s="5"/>
+      <c r="M100" s="5"/>
+      <c r="N100" s="9"/>
+    </row>
+    <row r="101" spans="4:14">
       <c r="D101" s="5"/>
-      <c r="E101" s="8"/>
-      <c r="F101" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="E101" s="10"/>
+      <c r="F101" s="10"/>
       <c r="G101" s="5" t="s">
-        <v>119</v>
+        <v>46</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I101" s="5"/>
+        <v>122</v>
+      </c>
+      <c r="I101" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J101" s="5"/>
       <c r="K101" s="5"/>
-      <c r="L101" s="11"/>
-    </row>
-    <row r="102" spans="3:12">
+      <c r="L101" s="5"/>
+      <c r="M101" s="5"/>
+      <c r="N101" s="9"/>
+    </row>
+    <row r="102" spans="3:14">
       <c r="C102" s="5">
         <v>36</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="E102" s="8"/>
-      <c r="F102" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="E102" s="10"/>
+      <c r="F102" s="10"/>
       <c r="G102" s="5" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I102" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="J102" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J102" s="5" t="s">
+        <v>124</v>
+      </c>
       <c r="K102" s="5"/>
-      <c r="L102" s="11"/>
-    </row>
-    <row r="103" spans="4:12">
+      <c r="L102" s="5"/>
+      <c r="M102" s="5"/>
+      <c r="N102" s="9"/>
+    </row>
+    <row r="103" spans="4:14">
       <c r="D103" s="5"/>
-      <c r="E103" s="8"/>
-      <c r="F103" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E103" s="10"/>
+      <c r="F103" s="10"/>
       <c r="G103" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H103" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J103" s="5"/>
-      <c r="K103" s="5"/>
-      <c r="L103" s="11"/>
-    </row>
-    <row r="104" spans="4:12">
+        <v>26</v>
+      </c>
+      <c r="I103" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L103" s="5"/>
+      <c r="M103" s="5"/>
+      <c r="N103" s="9"/>
+    </row>
+    <row r="104" ht="17" spans="4:14">
       <c r="D104" s="5"/>
-      <c r="E104" s="8"/>
-      <c r="F104" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="E104" s="10"/>
+      <c r="F104" s="10"/>
       <c r="G104" s="5" t="s">
-        <v>122</v>
+        <v>46</v>
       </c>
       <c r="H104" s="5" t="s">
-        <v>17</v>
+        <v>125</v>
       </c>
       <c r="I104" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J104" s="5"/>
+        <v>20</v>
+      </c>
+      <c r="J104" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="K104" s="5"/>
-      <c r="L104" s="11" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="105" spans="3:12">
+      <c r="L104" s="5"/>
+      <c r="M104" s="5"/>
+      <c r="N104" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="105" spans="3:14">
       <c r="C105" s="5">
         <v>37</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="E105" s="8"/>
-      <c r="F105" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="E105" s="10"/>
+      <c r="F105" s="10"/>
       <c r="G105" s="5" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="H105" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I105" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="I105" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="J105" s="5"/>
       <c r="K105" s="5"/>
-      <c r="L105" s="11"/>
-    </row>
-    <row r="106" spans="4:12">
+      <c r="L105" s="5"/>
+      <c r="M105" s="5"/>
+      <c r="N105" s="9"/>
+    </row>
+    <row r="106" ht="17" spans="4:14">
       <c r="D106" s="5"/>
-      <c r="E106" s="8"/>
-      <c r="F106" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E106" s="10"/>
+      <c r="F106" s="10"/>
       <c r="G106" s="5" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="H106" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="J106" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J106" s="5" t="s">
+        <v>128</v>
+      </c>
       <c r="K106" s="5"/>
-      <c r="L106" s="11" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="107" spans="4:12">
+      <c r="L106" s="5"/>
+      <c r="M106" s="5"/>
+      <c r="N106" s="9" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="107" spans="4:14">
       <c r="D107" s="5"/>
-      <c r="E107" s="8"/>
-      <c r="F107" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E107" s="10"/>
+      <c r="F107" s="10"/>
       <c r="G107" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J107" s="5"/>
-      <c r="K107" s="5"/>
-      <c r="L107" s="11"/>
-    </row>
-    <row r="108" spans="3:12">
+        <v>26</v>
+      </c>
+      <c r="I107" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L107" s="5"/>
+      <c r="M107" s="5"/>
+      <c r="N107" s="9"/>
+    </row>
+    <row r="108" spans="3:14">
       <c r="C108" s="5">
         <v>38</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="E108" s="8"/>
-      <c r="F108" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="E108" s="10"/>
+      <c r="F108" s="10"/>
       <c r="G108" s="5" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="H108" s="5" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="I108" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J108" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J108" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="K108" s="5"/>
-      <c r="L108" s="11"/>
-    </row>
-    <row r="109" spans="4:12">
+      <c r="L108" s="5"/>
+      <c r="M108" s="5"/>
+      <c r="N108" s="9"/>
+    </row>
+    <row r="109" spans="4:14">
       <c r="D109" s="5"/>
-      <c r="E109" s="8"/>
-      <c r="F109" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E109" s="10"/>
+      <c r="F109" s="10"/>
       <c r="G109" s="5" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H109" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I109" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="I109" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J109" s="5"/>
       <c r="K109" s="5"/>
-      <c r="L109" s="11"/>
-    </row>
-    <row r="110" spans="4:12">
+      <c r="L109" s="5"/>
+      <c r="M109" s="5"/>
+      <c r="N109" s="9"/>
+    </row>
+    <row r="110" spans="4:14">
       <c r="D110" s="5"/>
-      <c r="E110" s="8"/>
-      <c r="F110" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E110" s="10"/>
+      <c r="F110" s="10"/>
       <c r="G110" s="5" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="H110" s="5" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="I110" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="J110" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J110" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="K110" s="5"/>
-      <c r="L110" s="11"/>
-    </row>
-    <row r="111" spans="4:12">
+      <c r="L110" s="5"/>
+      <c r="M110" s="5"/>
+      <c r="N110" s="9"/>
+    </row>
+    <row r="111" spans="4:14">
       <c r="D111" s="5"/>
-      <c r="E111" s="8"/>
-      <c r="F111" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E111" s="10"/>
+      <c r="F111" s="10"/>
       <c r="G111" s="5" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="H111" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I111" s="5"/>
+        <v>58</v>
+      </c>
+      <c r="I111" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J111" s="5"/>
       <c r="K111" s="5"/>
-      <c r="L111" s="11"/>
-    </row>
-    <row r="112" spans="4:12">
+      <c r="L111" s="5"/>
+      <c r="M111" s="5"/>
+      <c r="N111" s="9"/>
+    </row>
+    <row r="112" spans="4:14">
       <c r="D112" s="5"/>
-      <c r="E112" s="8"/>
-      <c r="F112" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E112" s="10"/>
+      <c r="F112" s="10"/>
       <c r="G112" s="5" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="H112" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I112" s="5"/>
+        <v>59</v>
+      </c>
+      <c r="I112" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J112" s="5"/>
       <c r="K112" s="5"/>
-      <c r="L112" s="11"/>
-    </row>
-    <row r="113" spans="4:12">
+      <c r="L112" s="5"/>
+      <c r="M112" s="5"/>
+      <c r="N112" s="9"/>
+    </row>
+    <row r="113" ht="17" spans="4:14">
       <c r="D113" s="5"/>
-      <c r="E113" s="8"/>
-      <c r="F113" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="E113" s="10"/>
+      <c r="F113" s="10"/>
       <c r="G113" s="5" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="H113" s="5" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="I113" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J113" s="5"/>
+        <v>20</v>
+      </c>
+      <c r="J113" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="K113" s="5"/>
-      <c r="L113" s="11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="114" spans="3:12">
+      <c r="L113" s="5"/>
+      <c r="M113" s="5"/>
+      <c r="N113" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="114" spans="3:14">
       <c r="C114" s="5">
         <v>39</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="E114" s="8"/>
-      <c r="F114" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="E114" s="10"/>
+      <c r="F114" s="10"/>
       <c r="G114" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H114" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I114" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="H114" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I114" s="5"/>
       <c r="J114" s="5"/>
       <c r="K114" s="5"/>
-      <c r="L114" s="11"/>
-    </row>
-    <row r="115" spans="4:12">
+      <c r="L114" s="5"/>
+      <c r="M114" s="5"/>
+      <c r="N114" s="9"/>
+    </row>
+    <row r="115" spans="4:14">
       <c r="D115" s="5"/>
-      <c r="E115" s="8"/>
-      <c r="F115" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E115" s="10"/>
+      <c r="F115" s="10"/>
       <c r="G115" s="5" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="H115" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I115" s="5"/>
+        <v>56</v>
+      </c>
+      <c r="I115" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="J115" s="5"/>
       <c r="K115" s="5"/>
-      <c r="L115" s="11"/>
-    </row>
-    <row r="116" spans="4:12">
+      <c r="L115" s="5"/>
+      <c r="M115" s="5"/>
+      <c r="N115" s="9"/>
+    </row>
+    <row r="116" spans="4:14">
       <c r="D116" s="5"/>
-      <c r="E116" s="8"/>
-      <c r="F116" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E116" s="10"/>
+      <c r="F116" s="10"/>
       <c r="G116" s="5" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H116" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I116" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="I116" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J116" s="5"/>
       <c r="K116" s="5"/>
-      <c r="L116" s="11"/>
-    </row>
-    <row r="117" spans="4:12">
+      <c r="L116" s="5"/>
+      <c r="M116" s="5"/>
+      <c r="N116" s="9"/>
+    </row>
+    <row r="117" spans="4:14">
       <c r="D117" s="5"/>
-      <c r="E117" s="8"/>
-      <c r="F117" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E117" s="10"/>
+      <c r="F117" s="10"/>
       <c r="G117" s="5" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="H117" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I117" s="5"/>
+        <v>58</v>
+      </c>
+      <c r="I117" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J117" s="5"/>
       <c r="K117" s="5"/>
-      <c r="L117" s="11"/>
-    </row>
-    <row r="118" spans="4:12">
+      <c r="L117" s="5"/>
+      <c r="M117" s="5"/>
+      <c r="N117" s="9"/>
+    </row>
+    <row r="118" spans="4:14">
       <c r="D118" s="5"/>
-      <c r="E118" s="8"/>
-      <c r="F118" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E118" s="10"/>
+      <c r="F118" s="10"/>
       <c r="G118" s="5" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="H118" s="5" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="I118" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J118" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J118" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="K118" s="5"/>
-      <c r="L118" s="11"/>
-    </row>
-    <row r="119" spans="4:12">
+      <c r="L118" s="5"/>
+      <c r="M118" s="5"/>
+      <c r="N118" s="9"/>
+    </row>
+    <row r="119" spans="4:14">
       <c r="D119" s="5"/>
-      <c r="E119" s="8"/>
-      <c r="F119" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E119" s="10"/>
+      <c r="F119" s="10"/>
       <c r="G119" s="5" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="H119" s="5" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="I119" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J119" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J119" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="K119" s="5"/>
-      <c r="L119" s="11"/>
-    </row>
-    <row r="120" spans="4:12">
+      <c r="L119" s="5"/>
+      <c r="M119" s="5"/>
+      <c r="N119" s="9"/>
+    </row>
+    <row r="120" spans="4:14">
       <c r="D120" s="5"/>
-      <c r="E120" s="8"/>
-      <c r="F120" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E120" s="10"/>
+      <c r="F120" s="10"/>
       <c r="G120" s="5" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I120" s="5"/>
+        <v>59</v>
+      </c>
+      <c r="I120" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J120" s="5"/>
       <c r="K120" s="5"/>
-      <c r="L120" s="11"/>
-    </row>
-    <row r="121" spans="3:11">
+      <c r="L120" s="5"/>
+      <c r="M120" s="5"/>
+      <c r="N120" s="9"/>
+    </row>
+    <row r="121" spans="3:13">
       <c r="C121" s="5">
         <v>40</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E121" s="8"/>
-      <c r="F121" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="E121" s="10"/>
+      <c r="F121" s="10"/>
       <c r="G121" s="5" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="H121" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I121" s="5">
+        <v>64</v>
+      </c>
+      <c r="I121" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J121" s="5">
         <v>123456</v>
       </c>
-      <c r="J121" s="5"/>
       <c r="K121" s="5"/>
-    </row>
-    <row r="122" spans="4:12">
+      <c r="L121" s="5"/>
+      <c r="M121" s="5"/>
+    </row>
+    <row r="122" spans="4:14">
       <c r="D122" s="5"/>
-      <c r="E122" s="8"/>
-      <c r="F122" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E122" s="10"/>
+      <c r="F122" s="10"/>
       <c r="G122" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I122" s="5"/>
+        <v>26</v>
+      </c>
+      <c r="I122" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J122" s="5"/>
       <c r="K122" s="5"/>
-      <c r="L122" s="11"/>
-    </row>
-    <row r="123" spans="4:12">
+      <c r="L122" s="5"/>
+      <c r="M122" s="5"/>
+      <c r="N122" s="9"/>
+    </row>
+    <row r="123" ht="17" spans="4:14">
       <c r="D123" s="5"/>
-      <c r="E123" s="8"/>
-      <c r="F123" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="E123" s="10"/>
+      <c r="F123" s="10"/>
       <c r="G123" s="5" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="H123" s="5" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="I123" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J123" s="5"/>
+        <v>20</v>
+      </c>
+      <c r="J123" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="K123" s="5"/>
-      <c r="L123" s="11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="124" spans="3:12">
+      <c r="L123" s="5"/>
+      <c r="M123" s="5"/>
+      <c r="N123" s="9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="124" spans="3:14">
       <c r="C124" s="5">
         <v>41</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="E124" s="8"/>
-      <c r="F124" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="E124" s="10"/>
+      <c r="F124" s="10"/>
       <c r="G124" s="5" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="H124" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I124" s="5"/>
+        <v>64</v>
+      </c>
+      <c r="I124" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="J124" s="5"/>
       <c r="K124" s="5"/>
-      <c r="L124" s="11"/>
-    </row>
-    <row r="125" ht="49.5" spans="4:14">
+      <c r="L124" s="5"/>
+      <c r="M124" s="5"/>
+      <c r="N124" s="9"/>
+    </row>
+    <row r="125" ht="68" spans="4:16">
       <c r="D125" s="5"/>
-      <c r="E125" s="8"/>
-      <c r="F125" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E125" s="10"/>
+      <c r="F125" s="10"/>
       <c r="G125" s="5" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="H125" s="5" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="I125" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="J125" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J125" s="5" t="s">
+        <v>68</v>
+      </c>
       <c r="K125" s="5"/>
-      <c r="L125" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="N125" s="3">
+      <c r="L125" s="5"/>
+      <c r="M125" s="5"/>
+      <c r="N125" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="P125" s="3">
         <v>8</v>
       </c>
     </row>
-    <row r="126" spans="4:12">
+    <row r="126" spans="4:14">
       <c r="D126" s="5"/>
-      <c r="E126" s="8"/>
-      <c r="F126" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E126" s="10"/>
+      <c r="F126" s="10"/>
       <c r="G126" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H126" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I126" s="5"/>
+        <v>26</v>
+      </c>
+      <c r="I126" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J126" s="5"/>
       <c r="K126" s="5"/>
-      <c r="L126" s="11"/>
-    </row>
-    <row r="127" customFormat="1" spans="3:12">
+      <c r="L126" s="5"/>
+      <c r="M126" s="5"/>
+      <c r="N126" s="9"/>
+    </row>
+    <row r="127" customFormat="1" spans="3:14">
       <c r="C127" s="5">
         <v>42</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E127" s="8"/>
-      <c r="F127" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="E127" s="10"/>
+      <c r="F127" s="10"/>
       <c r="G127" s="5" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="H127" s="5" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="I127" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="J127" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J127" s="5" t="s">
+        <v>72</v>
+      </c>
       <c r="K127" s="5"/>
-      <c r="L127" s="11"/>
-    </row>
-    <row r="128" customFormat="1" spans="3:12">
+      <c r="L127" s="5"/>
+      <c r="M127" s="5"/>
+      <c r="N127" s="9"/>
+    </row>
+    <row r="128" customFormat="1" spans="3:14">
       <c r="C128" s="5"/>
       <c r="D128" s="5"/>
-      <c r="E128" s="8"/>
-      <c r="F128" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E128" s="10"/>
+      <c r="F128" s="10"/>
       <c r="G128" s="5" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="H128" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I128" s="5"/>
+        <v>73</v>
+      </c>
+      <c r="I128" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J128" s="5"/>
       <c r="K128" s="5"/>
-      <c r="L128" s="11"/>
-    </row>
-    <row r="129" customFormat="1" spans="3:12">
+      <c r="L128" s="5"/>
+      <c r="M128" s="5"/>
+      <c r="N128" s="9"/>
+    </row>
+    <row r="129" customFormat="1" spans="3:14">
       <c r="C129" s="5">
         <v>43</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E129" s="8"/>
-      <c r="F129" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="E129" s="10"/>
+      <c r="F129" s="10"/>
       <c r="G129" s="5" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="H129" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I129" s="5"/>
+        <v>77</v>
+      </c>
+      <c r="I129" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J129" s="5"/>
       <c r="K129" s="5"/>
-      <c r="L129" s="11"/>
-    </row>
-    <row r="130" customFormat="1" spans="3:12">
+      <c r="L129" s="5"/>
+      <c r="M129" s="5"/>
+      <c r="N129" s="9"/>
+    </row>
+    <row r="130" customFormat="1" spans="3:14">
       <c r="C130" s="5">
         <v>44</v>
       </c>
       <c r="D130" s="5"/>
-      <c r="E130" s="8"/>
-      <c r="F130" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E130" s="10"/>
+      <c r="F130" s="10"/>
       <c r="G130" s="5" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="H130" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I130" s="5"/>
+        <v>78</v>
+      </c>
+      <c r="I130" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J130" s="5"/>
       <c r="K130" s="5"/>
-      <c r="L130" s="11"/>
-    </row>
-    <row r="131" customFormat="1" spans="3:12">
+      <c r="L130" s="5"/>
+      <c r="M130" s="5"/>
+      <c r="N130" s="9"/>
+    </row>
+    <row r="131" customFormat="1" spans="3:14">
       <c r="C131" s="5">
         <v>45</v>
       </c>
       <c r="D131" s="5"/>
-      <c r="E131" s="8"/>
-      <c r="F131" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E131" s="10"/>
+      <c r="F131" s="10"/>
       <c r="G131" s="5" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="H131" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I131" s="5"/>
+        <v>79</v>
+      </c>
+      <c r="I131" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J131" s="5"/>
       <c r="K131" s="5"/>
-      <c r="L131" s="11"/>
-    </row>
-    <row r="132" s="4" customFormat="1" spans="3:12">
-      <c r="C132" s="9">
+      <c r="L131" s="5"/>
+      <c r="M131" s="5"/>
+      <c r="N131" s="9"/>
+    </row>
+    <row r="132" s="4" customFormat="1" spans="3:14">
+      <c r="C132" s="8">
         <v>46</v>
       </c>
-      <c r="D132" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="E132" s="10"/>
-      <c r="F132" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G132" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="H132" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="I132" s="9"/>
-      <c r="J132" s="9"/>
-      <c r="K132" s="9"/>
-      <c r="L132" s="13"/>
-    </row>
-    <row r="133" customFormat="1" spans="3:12">
+      <c r="D132" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E132" s="11"/>
+      <c r="F132" s="11"/>
+      <c r="G132" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H132" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I132" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="J132" s="8"/>
+      <c r="K132" s="8"/>
+      <c r="L132" s="8"/>
+      <c r="M132" s="8"/>
+      <c r="N132" s="13"/>
+    </row>
+    <row r="133" customFormat="1" spans="3:14">
       <c r="C133" s="5">
         <v>47</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="E133" s="8"/>
-      <c r="F133" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G133" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H133" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I133" s="3"/>
-      <c r="J133" s="5"/>
-      <c r="K133" s="5"/>
-      <c r="L133" s="11"/>
-    </row>
-    <row r="134" customFormat="1" spans="3:12">
+        <v>119</v>
+      </c>
+      <c r="E133" s="10"/>
+      <c r="F133" s="10"/>
+      <c r="G133" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H133" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I133" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J133" s="3"/>
+      <c r="K133" s="3"/>
+      <c r="L133" s="5"/>
+      <c r="M133" s="5"/>
+      <c r="N133" s="9"/>
+    </row>
+    <row r="134" customFormat="1" spans="3:14">
       <c r="C134" s="5">
         <v>48</v>
       </c>
       <c r="D134" s="5"/>
-      <c r="E134" s="8"/>
-      <c r="F134" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E134" s="10"/>
+      <c r="F134" s="10"/>
       <c r="G134" s="5" t="s">
-        <v>118</v>
+        <v>18</v>
       </c>
       <c r="H134" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I134" s="5">
+        <v>121</v>
+      </c>
+      <c r="I134" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J134" s="5">
         <v>63</v>
       </c>
-      <c r="J134" s="5"/>
       <c r="K134" s="5"/>
-      <c r="L134" s="11"/>
-    </row>
-    <row r="135" customFormat="1" spans="3:12">
+      <c r="L134" s="5"/>
+      <c r="M134" s="5"/>
+      <c r="N134" s="9"/>
+    </row>
+    <row r="135" customFormat="1" spans="3:14">
       <c r="C135" s="5">
         <v>49</v>
       </c>
       <c r="D135" s="5"/>
-      <c r="E135" s="8"/>
-      <c r="F135" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="E135" s="10"/>
+      <c r="F135" s="10"/>
       <c r="G135" s="5" t="s">
-        <v>119</v>
+        <v>46</v>
       </c>
       <c r="H135" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I135" s="5"/>
+        <v>122</v>
+      </c>
+      <c r="I135" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J135" s="5"/>
       <c r="K135" s="5"/>
-      <c r="L135" s="11"/>
-    </row>
-    <row r="136" customFormat="1" spans="3:12">
+      <c r="L135" s="5"/>
+      <c r="M135" s="5"/>
+      <c r="N135" s="9"/>
+    </row>
+    <row r="136" customFormat="1" spans="3:14">
       <c r="C136" s="5">
         <v>50</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="E136" s="8"/>
-      <c r="F136" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="E136" s="10"/>
+      <c r="F136" s="10"/>
       <c r="G136" s="5" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="H136" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I136" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="I136" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="J136" s="5"/>
       <c r="K136" s="5"/>
-      <c r="L136" s="11"/>
-    </row>
-    <row r="137" customFormat="1" spans="3:12">
+      <c r="L136" s="5"/>
+      <c r="M136" s="5"/>
+      <c r="N136" s="9"/>
+    </row>
+    <row r="137" customFormat="1" spans="3:14">
       <c r="C137" s="5">
         <v>51</v>
       </c>
       <c r="D137" s="5"/>
-      <c r="E137" s="8"/>
-      <c r="F137" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E137" s="10"/>
+      <c r="F137" s="10"/>
       <c r="G137" s="5" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="H137" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I137" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="J137" s="5"/>
-      <c r="K137" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="L137" s="11"/>
-    </row>
-    <row r="138" customFormat="1" spans="3:12">
+        <v>44</v>
+      </c>
+      <c r="J137" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="K137" s="5"/>
+      <c r="L137" s="5"/>
+      <c r="M137" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="N137" s="9"/>
+    </row>
+    <row r="138" customFormat="1" spans="3:14">
       <c r="C138" s="5">
         <v>52</v>
       </c>
       <c r="D138" s="5"/>
-      <c r="E138" s="8"/>
-      <c r="F138" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E138" s="10"/>
+      <c r="F138" s="10"/>
       <c r="G138" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H138" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I138" s="5"/>
+        <v>26</v>
+      </c>
+      <c r="I138" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J138" s="5"/>
       <c r="K138" s="5"/>
-      <c r="L138" s="11"/>
-    </row>
-    <row r="139" customFormat="1" spans="3:12">
+      <c r="L138" s="5"/>
+      <c r="M138" s="5"/>
+      <c r="N138" s="9"/>
+    </row>
+    <row r="139" customFormat="1" spans="3:14">
       <c r="C139" s="5">
         <v>53</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="E139" s="8"/>
-      <c r="F139" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="E139" s="10"/>
+      <c r="F139" s="10"/>
       <c r="G139" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H139" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I139" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="H139" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I139" s="5"/>
       <c r="J139" s="5"/>
       <c r="K139" s="5"/>
-      <c r="L139" s="11"/>
-    </row>
-    <row r="140" customFormat="1" spans="3:12">
+      <c r="L139" s="5"/>
+      <c r="M139" s="5"/>
+      <c r="N139" s="9"/>
+    </row>
+    <row r="140" customFormat="1" spans="3:14">
       <c r="C140" s="5"/>
       <c r="D140" s="5"/>
-      <c r="E140" s="8"/>
-      <c r="F140" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E140" s="10"/>
+      <c r="F140" s="10"/>
       <c r="G140" s="5" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="H140" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I140" s="5"/>
+        <v>56</v>
+      </c>
+      <c r="I140" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="J140" s="5"/>
       <c r="K140" s="5"/>
-      <c r="L140" s="11"/>
-    </row>
-    <row r="141" customFormat="1" spans="3:12">
+      <c r="L140" s="5"/>
+      <c r="M140" s="5"/>
+      <c r="N140" s="9"/>
+    </row>
+    <row r="141" customFormat="1" spans="3:14">
       <c r="C141" s="5"/>
       <c r="D141" s="5"/>
-      <c r="E141" s="8"/>
-      <c r="F141" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E141" s="10"/>
+      <c r="F141" s="10"/>
       <c r="G141" s="5" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H141" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I141" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="I141" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J141" s="5"/>
       <c r="K141" s="5"/>
-      <c r="L141" s="11"/>
-    </row>
-    <row r="142" customFormat="1" spans="3:12">
+      <c r="L141" s="5"/>
+      <c r="M141" s="5"/>
+      <c r="N141" s="9"/>
+    </row>
+    <row r="142" customFormat="1" spans="3:14">
       <c r="C142" s="5"/>
       <c r="D142" s="5"/>
-      <c r="E142" s="8"/>
-      <c r="F142" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E142" s="10"/>
+      <c r="F142" s="10"/>
       <c r="G142" s="5" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="H142" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I142" s="5"/>
+        <v>58</v>
+      </c>
+      <c r="I142" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J142" s="5"/>
       <c r="K142" s="5"/>
-      <c r="L142" s="11"/>
-    </row>
-    <row r="143" customFormat="1" spans="3:12">
+      <c r="L142" s="5"/>
+      <c r="M142" s="5"/>
+      <c r="N142" s="9"/>
+    </row>
+    <row r="143" customFormat="1" spans="3:14">
       <c r="C143" s="5"/>
       <c r="D143" s="5"/>
-      <c r="E143" s="8"/>
-      <c r="F143" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E143" s="10"/>
+      <c r="F143" s="10"/>
       <c r="G143" s="5" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="H143" s="5" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="I143" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J143" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J143" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="K143" s="5"/>
-      <c r="L143" s="11"/>
-    </row>
-    <row r="144" customFormat="1" spans="3:12">
+      <c r="L143" s="5"/>
+      <c r="M143" s="5"/>
+      <c r="N143" s="9"/>
+    </row>
+    <row r="144" customFormat="1" spans="3:14">
       <c r="C144" s="5"/>
       <c r="D144" s="5"/>
-      <c r="E144" s="8"/>
-      <c r="F144" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E144" s="10"/>
+      <c r="F144" s="10"/>
       <c r="G144" s="5" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="H144" s="5" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="I144" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J144" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J144" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="K144" s="5"/>
-      <c r="L144" s="11"/>
-    </row>
-    <row r="145" customFormat="1" spans="3:12">
+      <c r="L144" s="5"/>
+      <c r="M144" s="5"/>
+      <c r="N144" s="9"/>
+    </row>
+    <row r="145" customFormat="1" spans="3:14">
       <c r="C145" s="5"/>
       <c r="D145" s="5"/>
-      <c r="E145" s="8"/>
-      <c r="F145" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E145" s="10"/>
+      <c r="F145" s="10"/>
       <c r="G145" s="5" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="H145" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I145" s="5"/>
+        <v>59</v>
+      </c>
+      <c r="I145" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J145" s="5"/>
       <c r="K145" s="5"/>
-      <c r="L145" s="11"/>
-    </row>
-    <row r="146" customFormat="1" spans="3:12">
+      <c r="L145" s="5"/>
+      <c r="M145" s="5"/>
+      <c r="N145" s="9"/>
+    </row>
+    <row r="146" customFormat="1" spans="3:14">
       <c r="C146" s="5">
         <v>54</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="E146" s="8"/>
-      <c r="F146" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="E146" s="10"/>
+      <c r="F146" s="10"/>
       <c r="G146" s="5" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="H146" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I146" s="5"/>
+        <v>64</v>
+      </c>
+      <c r="I146" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="J146" s="5"/>
       <c r="K146" s="5"/>
-      <c r="L146" s="11"/>
-    </row>
-    <row r="147" customFormat="1" ht="49.5" spans="3:12">
+      <c r="L146" s="5"/>
+      <c r="M146" s="5"/>
+      <c r="N146" s="9"/>
+    </row>
+    <row r="147" customFormat="1" ht="68" spans="3:14">
       <c r="C147" s="5">
         <v>55</v>
       </c>
       <c r="D147" s="5"/>
-      <c r="E147" s="8"/>
-      <c r="F147" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E147" s="10"/>
+      <c r="F147" s="10"/>
       <c r="G147" s="5" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="H147" s="5" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="I147" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="J147" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J147" s="5" t="s">
+        <v>68</v>
+      </c>
       <c r="K147" s="5"/>
-      <c r="L147" s="11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="148" customFormat="1" spans="3:12">
+      <c r="L147" s="5"/>
+      <c r="M147" s="5"/>
+      <c r="N147" s="9" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="148" customFormat="1" spans="3:14">
       <c r="C148" s="5">
         <v>56</v>
       </c>
       <c r="D148" s="5"/>
-      <c r="E148" s="8"/>
-      <c r="F148" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E148" s="10"/>
+      <c r="F148" s="10"/>
       <c r="G148" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H148" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I148" s="5"/>
+        <v>26</v>
+      </c>
+      <c r="I148" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J148" s="5"/>
       <c r="K148" s="5"/>
-      <c r="L148" s="11"/>
-    </row>
-    <row r="149" s="3" customFormat="1" spans="3:12">
+      <c r="L148" s="5"/>
+      <c r="M148" s="5"/>
+      <c r="N148" s="9"/>
+    </row>
+    <row r="149" s="3" customFormat="1" spans="3:14">
       <c r="C149" s="5">
         <v>57</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="E149" s="8"/>
-      <c r="F149" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="E149" s="10"/>
+      <c r="F149" s="10"/>
       <c r="G149" s="5" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="H149" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I149" s="5"/>
+        <v>59</v>
+      </c>
+      <c r="I149" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J149" s="5"/>
       <c r="K149" s="5"/>
-      <c r="L149" s="11"/>
-    </row>
-    <row r="150" s="3" customFormat="1" spans="3:12">
+      <c r="L149" s="5"/>
+      <c r="M149" s="5"/>
+      <c r="N149" s="9"/>
+    </row>
+    <row r="150" s="3" customFormat="1" spans="3:14">
       <c r="C150" s="5">
         <v>58</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="E150" s="8"/>
-      <c r="F150" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="E150" s="10"/>
+      <c r="F150" s="10"/>
       <c r="G150" s="5" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="H150" s="5" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="I150" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="J150" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J150" s="5" t="s">
+        <v>85</v>
+      </c>
       <c r="K150" s="5"/>
-      <c r="L150" s="11"/>
-    </row>
-    <row r="151" s="3" customFormat="1" spans="3:12">
+      <c r="L150" s="5"/>
+      <c r="M150" s="5"/>
+      <c r="N150" s="9"/>
+    </row>
+    <row r="151" s="3" customFormat="1" spans="3:14">
       <c r="C151" s="5"/>
       <c r="D151" s="5"/>
-      <c r="E151" s="8"/>
-      <c r="F151" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E151" s="10"/>
+      <c r="F151" s="10"/>
       <c r="G151" s="5" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="H151" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I151" s="5"/>
+        <v>73</v>
+      </c>
+      <c r="I151" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J151" s="5"/>
       <c r="K151" s="5"/>
-      <c r="L151" s="11"/>
-    </row>
-    <row r="152" s="3" customFormat="1" spans="3:12">
+      <c r="L151" s="5"/>
+      <c r="M151" s="5"/>
+      <c r="N151" s="9"/>
+    </row>
+    <row r="152" s="3" customFormat="1" ht="17" spans="3:14">
       <c r="C152" s="5"/>
       <c r="D152" s="5"/>
-      <c r="E152" s="8"/>
-      <c r="F152" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="E152" s="10"/>
+      <c r="F152" s="10"/>
       <c r="G152" s="5" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="H152" s="5" t="s">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="I152" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J152" s="5"/>
+        <v>20</v>
+      </c>
+      <c r="J152" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="K152" s="5"/>
-      <c r="L152" s="11" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="153" s="3" customFormat="1" spans="3:12">
+      <c r="L152" s="5"/>
+      <c r="M152" s="5"/>
+      <c r="N152" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="153" s="3" customFormat="1" spans="3:14">
       <c r="C153" s="5">
         <v>59</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="E153" s="8"/>
-      <c r="F153" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="E153" s="10"/>
+      <c r="F153" s="10"/>
       <c r="G153" s="5" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="H153" s="5" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="I153" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="J153" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J153" s="5" t="s">
+        <v>89</v>
+      </c>
       <c r="K153" s="5"/>
-      <c r="L153" s="11"/>
-    </row>
-    <row r="154" s="3" customFormat="1" spans="3:12">
+      <c r="L153" s="5"/>
+      <c r="M153" s="5"/>
+      <c r="N153" s="9"/>
+    </row>
+    <row r="154" s="3" customFormat="1" spans="3:14">
       <c r="C154" s="5"/>
       <c r="D154" s="5"/>
-      <c r="E154" s="8"/>
-      <c r="F154" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E154" s="10"/>
+      <c r="F154" s="10"/>
       <c r="G154" s="5" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="H154" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="I154" s="5"/>
+        <v>73</v>
+      </c>
+      <c r="I154" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="J154" s="5"/>
       <c r="K154" s="5"/>
-      <c r="L154" s="11" t="b">
+      <c r="L154" s="5"/>
+      <c r="M154" s="5"/>
+      <c r="N154" s="9" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="155" s="3" customFormat="1" spans="3:12">
+    <row r="155" s="3" customFormat="1" spans="3:14">
       <c r="C155" s="5">
         <v>60</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="E155" s="8"/>
-      <c r="F155" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="E155" s="10"/>
+      <c r="F155" s="10"/>
       <c r="G155" s="5" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="H155" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="J155" s="5"/>
-      <c r="K155" s="5"/>
-      <c r="L155" s="11"/>
-    </row>
-    <row r="156" s="3" customFormat="1" spans="3:12">
+        <v>71</v>
+      </c>
+      <c r="I155" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L155" s="5"/>
+      <c r="M155" s="5"/>
+      <c r="N155" s="9"/>
+    </row>
+    <row r="156" s="3" customFormat="1" spans="3:14">
       <c r="C156" s="5"/>
       <c r="D156" s="5"/>
-      <c r="E156" s="8"/>
-      <c r="F156" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E156" s="10"/>
+      <c r="F156" s="10"/>
       <c r="G156" s="5" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="H156" s="5" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="I156" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="J156" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J156" s="5" t="s">
+        <v>141</v>
+      </c>
       <c r="K156" s="5"/>
-      <c r="L156" s="11"/>
-    </row>
-    <row r="157" s="3" customFormat="1" spans="3:12">
+      <c r="L156" s="5"/>
+      <c r="M156" s="5"/>
+      <c r="N156" s="9"/>
+    </row>
+    <row r="157" s="3" customFormat="1" spans="3:14">
       <c r="C157" s="5"/>
       <c r="D157" s="5"/>
-      <c r="E157" s="8"/>
-      <c r="F157" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E157" s="10"/>
+      <c r="F157" s="10"/>
       <c r="G157" s="5" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="H157" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I157" s="5"/>
+        <v>73</v>
+      </c>
+      <c r="I157" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J157" s="5"/>
       <c r="K157" s="5"/>
-      <c r="L157" s="11"/>
-    </row>
-    <row r="158" s="3" customFormat="1" ht="33" spans="3:12">
+      <c r="L157" s="5"/>
+      <c r="M157" s="5"/>
+      <c r="N157" s="9"/>
+    </row>
+    <row r="158" s="3" customFormat="1" ht="34" spans="3:14">
       <c r="C158" s="5"/>
       <c r="D158" s="5"/>
-      <c r="E158" s="8"/>
-      <c r="F158" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="E158" s="10"/>
+      <c r="F158" s="10"/>
       <c r="G158" s="5" t="s">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="H158" s="5" t="s">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="I158" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J158" s="5"/>
+        <v>20</v>
+      </c>
+      <c r="J158" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="K158" s="5"/>
-      <c r="L158" s="11" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="159" s="3" customFormat="1" spans="3:12">
+      <c r="L158" s="5"/>
+      <c r="M158" s="5"/>
+      <c r="N158" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="159" s="3" customFormat="1" spans="3:14">
       <c r="C159" s="5">
         <v>61</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="E159" s="8"/>
-      <c r="F159" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="E159" s="10"/>
+      <c r="F159" s="10"/>
       <c r="G159" s="5" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="H159" s="5" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="I159" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="J159" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J159" s="5" t="s">
+        <v>72</v>
+      </c>
       <c r="K159" s="5"/>
-      <c r="L159" s="11"/>
-    </row>
-    <row r="160" s="3" customFormat="1" spans="3:12">
+      <c r="L159" s="5"/>
+      <c r="M159" s="5"/>
+      <c r="N159" s="9"/>
+    </row>
+    <row r="160" s="3" customFormat="1" spans="3:14">
       <c r="C160" s="5"/>
       <c r="D160" s="5"/>
-      <c r="E160" s="8"/>
-      <c r="F160" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E160" s="10"/>
+      <c r="F160" s="10"/>
       <c r="G160" s="5" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="H160" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I160" s="5"/>
+        <v>73</v>
+      </c>
+      <c r="I160" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="J160" s="5"/>
       <c r="K160" s="5"/>
-      <c r="L160" s="11"/>
-    </row>
-    <row r="161" s="2" customFormat="1" spans="3:12">
-      <c r="C161" s="9">
+      <c r="L160" s="5"/>
+      <c r="M160" s="5"/>
+      <c r="N160" s="9"/>
+    </row>
+    <row r="161" s="2" customFormat="1" spans="3:14">
+      <c r="C161" s="8">
         <v>62</v>
       </c>
-      <c r="D161" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E161" s="10"/>
-      <c r="F161" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G161" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H161" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="I161" s="9"/>
-      <c r="J161" s="9"/>
-      <c r="K161" s="9"/>
-      <c r="L161" s="13"/>
-    </row>
-    <row r="162" s="2" customFormat="1" spans="3:12">
-      <c r="C162" s="9"/>
-      <c r="D162" s="9"/>
-      <c r="E162" s="10"/>
-      <c r="F162" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G162" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H162" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="I162" s="9"/>
-      <c r="J162" s="9"/>
-      <c r="K162" s="9"/>
-      <c r="L162" s="13"/>
-    </row>
-    <row r="163" s="2" customFormat="1" spans="3:12">
-      <c r="C163" s="9"/>
-      <c r="D163" s="9"/>
-      <c r="E163" s="10"/>
-      <c r="F163" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G163" s="9" t="s">
+      <c r="D161" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="H163" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="I163" s="9"/>
-      <c r="J163" s="9"/>
-      <c r="K163" s="9"/>
-      <c r="L163" s="13"/>
+      <c r="E161" s="11"/>
+      <c r="F161" s="11"/>
+      <c r="G161" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H161" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="I161" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="J161" s="8"/>
+      <c r="K161" s="8"/>
+      <c r="L161" s="8"/>
+      <c r="M161" s="8"/>
+      <c r="N161" s="13"/>
+    </row>
+    <row r="162" s="2" customFormat="1" spans="3:14">
+      <c r="C162" s="8"/>
+      <c r="D162" s="8"/>
+      <c r="E162" s="11"/>
+      <c r="F162" s="11"/>
+      <c r="G162" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H162" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="I162" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="J162" s="8"/>
+      <c r="K162" s="8"/>
+      <c r="L162" s="8"/>
+      <c r="M162" s="8"/>
+      <c r="N162" s="13"/>
+    </row>
+    <row r="163" s="2" customFormat="1" spans="3:14">
+      <c r="C163" s="8"/>
+      <c r="D163" s="8"/>
+      <c r="E163" s="11"/>
+      <c r="F163" s="11"/>
+      <c r="G163" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H163" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="I163" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="J163" s="8"/>
+      <c r="K163" s="8"/>
+      <c r="L163" s="8"/>
+      <c r="M163" s="8"/>
+      <c r="N163" s="13"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G$1:G$1048576">
       <formula1>"id,xpath,accessibility_id,android_uiautomator,android_viewtag,android_data_matcher,android_view_matcher,ios_uiautomation,ios_predicate,ios_class_chain,class_name,link_text,css_selector,name"</formula1>
     </dataValidation>
   </dataValidations>
